--- a/docs/問題集ライブラリ総合目次.xlsx
+++ b/docs/問題集ライブラリ総合目次.xlsx
@@ -309,7 +309,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8953500" cy="5238750"/>
+    <ext cx="8953500" cy="5286375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -638,7 +638,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本ライブラリは、ゼネコン構造設計部の新入社員が RC マンションの構造設計を体系的に学ぶための図解つき問題集（全34冊＋風/地震/VEのMarkdown教材）です。各冊は『目次→図解つき内容→解答』の構成で、数値例はすべて検算済み。規準・告示に依存する値には『確認要』を明記しています。</t>
+          <t>本ライブラリは、ゼネコン構造設計部の新入社員が RC マンションの構造設計を体系的に学ぶための図解つき問題集（全35冊＋風/地震/VEのMarkdown教材）です。各冊は『目次→図解つき内容→解答』の構成で、数値例はすべて検算済み。規準・告示に依存する値には『確認要』を明記しています。</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1087,22 +1087,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ねじり検討</t>
+          <t>擁壁の設計 No.3</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>ねじりモーメント・Bach/Rausch</t>
+          <t>種類/土圧選別/安定計算/応力/配筋/排水</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>docs/torsion/</t>
+          <t>docs/retaining_wall_design/</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>ねじり検討問題集.xlsx</t>
+          <t>擁壁の設計問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1112,54 +1112,54 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>ねじり検討</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ねじりモーメント・Bach/Rausch</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>docs/torsion/</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>ねじり検討問題集.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>たわみ・層間変形角</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>変形増大率K・層間変形角</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>docs/deflection/</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>たわみ層間変形角問題集.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>D. 耐震設計（一次・二次設計）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>一次・二次設計</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>許容応力度/保有水平耐力の流れ</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>docs/seismic_design/</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>一次二次設計問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1169,22 +1169,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>剛床・移行せん断力</t>
+          <t>一次・二次設計</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>剛床仮定・移行せん断力</t>
+          <t>許容応力度/保有水平耐力の流れ</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>docs/diaphragm/</t>
+          <t>docs/seismic_design/</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>剛床移行せん断力問題集.xlsx</t>
+          <t>一次二次設計問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>偏心率・剛性率</t>
+          <t>剛床・移行せん断力</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Re&lt;=0.15・Rs&gt;=0.6・Fes</t>
+          <t>剛床仮定・移行せん断力</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>docs/eccentricity/</t>
+          <t>docs/diaphragm/</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>偏心率剛性率問題集.xlsx</t>
+          <t>剛床移行せん断力問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>保有水平耐力</t>
+          <t>偏心率・剛性率</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Qu&gt;=Qun=Ds・Fes・Qud</t>
+          <t>Re&lt;=0.15・Rs&gt;=0.6・Fes</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>docs/capacity/</t>
+          <t>docs/eccentricity/</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>保有水平耐力計算問題集.xlsx</t>
+          <t>偏心率剛性率問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1244,22 +1244,22 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>崩壊形</t>
+          <t>保有水平耐力</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>全体/部分/局部崩壊・強柱弱梁</t>
+          <t>Qu&gt;=Qun=Ds・Fes・Qud</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>docs/collapse/</t>
+          <t>docs/capacity/</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>崩壊形問題集.xlsx</t>
+          <t>保有水平耐力計算問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1269,22 +1269,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>部材種別</t>
+          <t>崩壊形</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>FA〜FD・Ds値</t>
+          <t>全体/部分/局部崩壊・強柱弱梁</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>docs/member_class/</t>
+          <t>docs/collapse/</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>部材種別問題集.xlsx</t>
+          <t>崩壊形問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1294,86 +1294,86 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
+          <t>部材種別</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>FA〜FD・Ds値</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>docs/member_class/</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>部材種別問題集.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>保証設計</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>せん断余裕率・曲げ先行</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>docs/shear_margin/</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>保証設計問題集.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>E. 荷重・外力</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>土圧</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>静止/主働/受働土圧・Ka/Kp</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>docs/earth_pressure/</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>土圧問題集.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>F. 地盤・地盤調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>柱状図の読み取り</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>KBM・標高深度・N値・支持層判定</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>docs/borelog/</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>柱状図の読み取り問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1383,22 +1383,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>各地盤定数</t>
+          <t>柱状図の読み取り</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>N/φ/C/qu/Eo/FC/ρ/pc・換算式</t>
+          <t>KBM・標高深度・N値・支持層判定</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>docs/soil_params/</t>
+          <t>docs/borelog/</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>各地盤定数問題集.xlsx</t>
+          <t>柱状図の読み取り問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1408,54 +1408,54 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>各地盤定数</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>N/φ/C/qu/Eo/FC/ρ/pc・換算式</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>docs/soil_params/</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>各地盤定数問題集.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>液状化判定</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>FL/PL/Dcy・地盤定数低減</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>docs/liquefaction/</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>液状化判定問題集.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>G. 支持力・基礎形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>地盤の支持力(Terzaghi)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>3項・支持力係数・砂/粘土</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>docs/bearing_terzaghi/</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>地盤の支持力Terzaghi問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1465,22 +1465,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>上下分離モデル</t>
+          <t>地盤の支持力(Terzaghi)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>分離/一体・支点条件・接地圧</t>
+          <t>3項・支持力係数・砂/粘土</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>docs/updown_model/</t>
+          <t>docs/bearing_terzaghi/</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>上下分離モデル問題集.xlsx</t>
+          <t>地盤の支持力Terzaghi問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1490,22 +1490,22 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>柱状改良の支持力</t>
+          <t>上下分離モデル</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>複合地盤/改良体式・改良率</t>
+          <t>分離/一体・支点条件・接地圧</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>docs/column_improve/</t>
+          <t>docs/updown_model/</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>柱状改良の支持力問題集.xlsx</t>
+          <t>上下分離モデル問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1515,54 +1515,54 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>柱状改良の支持力</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>複合地盤/改良体式・改良率</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>docs/column_improve/</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>柱状改良の支持力問題集.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>場所打ち杭の支持力</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>先端+周面・許容圧縮/引抜き</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>docs/castpile/</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>場所打ち杭の支持力問題集.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>H. 杭・基礎の設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>杭の水平力検討</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ばね支承梁・kh・M-N図・配筋</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>docs/pile_lateral/</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>杭の水平力検討問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1572,22 +1572,22 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>既成杭の計算書確認</t>
+          <t>杭の水平力検討</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>杭種類/工法・反力反映・干渉</t>
+          <t>ばね支承梁・kh・M-N図・配筋</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>docs/precast_pile/</t>
+          <t>docs/pile_lateral/</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>既成杭の計算書確認問題集.xlsx</t>
+          <t>杭の水平力検討問題集.xlsx</t>
         </is>
       </c>
     </row>
@@ -1597,20 +1597,45 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>既成杭の計算書確認</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>杭種類/工法・反力反映・干渉</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>docs/precast_pile/</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>既成杭の計算書確認問題集.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>基礎フーチング設計</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>地反力/杭反力・独立/べた/杭/偏心</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>docs/footing_design/</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>基礎フーチング設計問題集.xlsx</t>
         </is>
@@ -1618,13 +1643,13 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
